--- a/pptx/testdata/golden/06-chart-multi/ppt/embeddings/Microsoft_Excel_Worksheet2.xlsx
+++ b/pptx/testdata/golden/06-chart-multi/ppt/embeddings/Microsoft_Excel_Worksheet2.xlsx
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:C5'" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:C5" totalsRowShown="0">
   <tableColumns count="3">
     <tableColumn id="1" name="Column1"/>
     <tableColumn id="2" name="Series A"/>
